--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_382_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_382_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>19</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>5</v>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>48:54</t>
+          <t>28:52</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>37:17</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>42:17</t>
+          <t>22:15</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2235,22 +2235,22 @@
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>17.5%</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>14.2%</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>7.9%</t>
         </is>
       </c>
     </row>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>31:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,12 +2431,12 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>63:42</t>
+          <t>33:39</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>33.0%</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>21:33</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>04:01</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
@@ -3099,10 +3099,10 @@
         <v>26</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>50:21</t>
+          <t>30:18</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,22 +3215,22 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>20.4%</t>
         </is>
       </c>
     </row>
@@ -3295,10 +3295,10 @@
         <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>42:53</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>14.1%</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>31:53</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AN28" t="n">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3827,16 +3827,16 @@
         <v>95</v>
       </c>
       <c r="T30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>14</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>49:53</t>
+          <t>29:51</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>29.5%</t>
         </is>
       </c>
     </row>
@@ -4684,16 +4684,16 @@
         <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>3</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>56:27</t>
+          <t>26:24</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>35:19</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>50:40</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>48:14</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,17 +5976,17 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>16.8%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -6056,7 +6056,7 @@
         <v>10</v>
       </c>
       <c r="T44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>34:35</t>
+          <t>24:35</t>
         </is>
       </c>
       <c r="AN44" t="n">
@@ -6172,17 +6172,17 @@
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>40:42</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>9.2%</t>
         </is>
       </c>
     </row>
@@ -6454,10 +6454,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>5</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>59:24</t>
+          <t>29:21</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,22 +6564,22 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -6784,16 +6784,16 @@
         <v>73</v>
       </c>
       <c r="T48" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>25</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_382_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_382_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M3" t="n">
         <v>13</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,16 +1335,16 @@
         <v>19</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X17" t="n">
         <v>5</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3099,10 +3099,10 @@
         <v>26</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3295,10 +3295,10 @@
         <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -3494,7 +3494,7 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>95</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>14</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4684,16 +4684,16 @@
         <v>12</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>3</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>10</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -6255,13 +6255,13 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>6</v>
@@ -6454,10 +6454,10 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X46" t="n">
         <v>5</v>
@@ -6784,16 +6784,16 @@
         <v>73</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>25</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_382_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_382_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="O2" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="P2" t="n">
         <v>10</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -851,20 +851,20 @@
         <v>2</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" t="n">
         <v>7</v>
       </c>
-      <c r="V3" t="n">
-        <v>8</v>
-      </c>
       <c r="W3" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>80.65</t>
+          <t>60.00</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>30.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,10 +1347,10 @@
         <v>2</v>
       </c>
       <c r="X17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
@@ -2523,14 +2523,14 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA23" t="n">
@@ -2719,14 +2719,14 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -3307,14 +3307,14 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y27" t="n">
         <v>3</v>
       </c>
-      <c r="Y27" t="n">
-        <v>4</v>
-      </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Y30" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -4925,25 +4925,25 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y42" t="n">
         <v>4</v>
       </c>
-      <c r="Y42" t="n">
-        <v>5</v>
-      </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6068,14 +6068,14 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA44" t="n">
@@ -6264,14 +6264,14 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA45" t="n">
@@ -6300,18 +6300,18 @@
         <v>1</v>
       </c>
       <c r="AH45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ45" t="n">
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>1</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Y48" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>80.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH48" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
         <v>7</v>
       </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="AJ48" t="n">
-        <v>8</v>
-      </c>
       <c r="AK48" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
